--- a/branches/release-3.0.0/StructureDefinition-ereferral-servicerequest-nursing.xlsx
+++ b/branches/release-3.0.0/StructureDefinition-ereferral-servicerequest-nursing.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6527" uniqueCount="968">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6527" uniqueCount="969">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T14:55:19+00:00</t>
+    <t>2026-10-29T04:33:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-referral-servicerequest-nursing</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-referral-servicerequest-nursing</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -627,7 +627,7 @@
     <t>feedback</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-ext-feedback-to-prescriber}
+    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-ext-feedback-to-prescriber}
 </t>
   </si>
   <si>
@@ -647,7 +647,7 @@
     <t>validity</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-ext-validity-period}
+    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-ext-validity-period}
 </t>
   </si>
   <si>
@@ -663,7 +663,7 @@
     <t>latest</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-ext-latest-end-date}
+    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-ext-latest-end-date}
 </t>
   </si>
   <si>
@@ -679,7 +679,7 @@
     <t>performerType</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-ext-performer-type}
+    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-ext-performer-type}
 </t>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <t>statusReason</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {request-statusReason|5.3.0}
+    <t xml:space="preserve">Extension {request-statusReason|5.4.0}
 </t>
   </si>
   <si>
@@ -760,7 +760,7 @@
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/referral/ValueSet/be-vs-prescription-status-reason</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/drp/ValueSet/be-vs-prescription-status-reason</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -1006,7 +1006,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/referral/NamingSystem/uhmep</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/drp/NamingSystem/uhmep</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -1129,7 +1129,7 @@
     <t>ServiceRequest.identifier:SHORT.system</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/referral/NamingSystem/uhmep-short</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/drp/NamingSystem/uhmep-short</t>
   </si>
   <si>
     <t>ServiceRequest.identifier:SHORT.value</t>
@@ -1306,7 +1306,7 @@
     <t>This element is labeled as a modifier because the intent alters when and how the resource is actually applicable.</t>
   </si>
   <si>
-    <t>The actual valueset will be provided when a terminology package is available. For current guidance, see the included [ValueSet](https://www.ehealth.fgov.be/standards/fhir/referral/1.0.0/ValueSet-be-vs-request-intent.html).</t>
+    <t>The actual valueset will be provided when a terminology package is available. For current guidance, see the included [ValueSet](https://build.fhir.org/ig/hl7-be/referral-uhmep/ValueSet-be-vs-request-intent.html).</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/request-intent|4.0.1</t>
@@ -1375,7 +1375,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>Categories of care that can be prescribed. See [ValueSet](https://www.ehealth.fgov.be/standards/fhir/referral/1.0.0/ValueSet-be-vs-categories-of-care.html).</t>
+    <t>Categories of care that can be prescribed. See [ValueSet](https://build.fhir.org/ig/hl7-be/referral-uhmep/ValueSet-be-vs-categories-of-care.html).</t>
   </si>
   <si>
     <t>https://www.ehealth.fgov.be/standards/fhir/terminology/ValueSet/be-vs-categories-of-care</t>
@@ -1710,7 +1710,7 @@
     <t>Many laboratory and radiology procedure codes embed the specimen/organ system in the test order name, for example,  serum or serum/plasma glucose, or a chest x-ray. The specimen might not be recorded separately from the test code.</t>
   </si>
   <si>
-    <t>The actual valueset will be provided when a terminology package is available.</t>
+    <t>The actual valueset will be provided when a terminology package is available. For current guidance, see the included [ValueSet](https://build.fhir.org/ig/hl7-be/referral-uhmep/ValueSet-be-vs-requested-services-nurse.html).</t>
   </si>
   <si>
     <t>https://www.ehealth.fgov.be/standards/fhir/terminology/ValueSet/be-vs-nursing-care-requested</t>
@@ -1745,6 +1745,9 @@
   </si>
   <si>
     <t>For information from the medical record intended to support the delivery of the requested services, use the `supportingInformation` element.</t>
+  </si>
+  <si>
+    <t>The actual valueset will be provided when a terminology package is available. For current guidance, see the included [ValueSet](https://build.fhir.org/ig/hl7-be/referral-uhmep/ValueSet-be-vs-requested-services-nurse-detail.html).</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/servicerequest-orderdetail</t>
@@ -3360,7 +3363,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="176.984375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="181.6171875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="85.30859375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -14678,10 +14681,10 @@
         <v>156</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>547</v>
+        <v>559</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>81</v>
@@ -14708,7 +14711,7 @@
         <v>80</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>102</v>
@@ -14717,7 +14720,7 @@
         <v>81</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>551</v>
@@ -14731,10 +14734,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14846,10 +14849,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14961,10 +14964,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15080,10 +15083,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15195,10 +15198,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15312,10 +15315,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15431,10 +15434,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15548,10 +15551,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15665,10 +15668,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15782,10 +15785,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15901,10 +15904,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16020,10 +16023,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16046,17 +16049,17 @@
         <v>91</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>81</v>
@@ -16093,17 +16096,17 @@
         <v>81</v>
       </c>
       <c r="AB109" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AC109" s="2"/>
       <c r="AD109" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE109" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -16121,10 +16124,10 @@
         <v>81</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>81</v>
@@ -16135,13 +16138,13 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D110" t="s" s="2">
         <v>81</v>
@@ -16163,17 +16166,17 @@
         <v>91</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>81</v>
@@ -16222,7 +16225,7 @@
         <v>81</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -16240,10 +16243,10 @@
         <v>81</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>81</v>
@@ -16254,10 +16257,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16369,10 +16372,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16484,10 +16487,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16510,19 +16513,19 @@
         <v>91</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>81</v>
@@ -16571,7 +16574,7 @@
         <v>81</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -16589,10 +16592,10 @@
         <v>81</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>81</v>
@@ -16603,10 +16606,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16632,20 +16635,20 @@
         <v>166</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q114" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="R114" t="s" s="2">
         <v>81</v>
@@ -16669,10 +16672,10 @@
         <v>297</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>81</v>
@@ -16690,7 +16693,7 @@
         <v>81</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
@@ -16708,10 +16711,10 @@
         <v>81</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>81</v>
@@ -16722,10 +16725,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16751,14 +16754,14 @@
         <v>104</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>81</v>
@@ -16807,7 +16810,7 @@
         <v>81</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>79</v>
@@ -16825,10 +16828,10 @@
         <v>81</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AN115" t="s" s="2">
         <v>81</v>
@@ -16839,10 +16842,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16868,14 +16871,14 @@
         <v>132</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>81</v>
@@ -16924,7 +16927,7 @@
         <v>81</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
@@ -16933,7 +16936,7 @@
         <v>90</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AJ116" t="s" s="2">
         <v>102</v>
@@ -16942,10 +16945,10 @@
         <v>81</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>81</v>
@@ -16956,10 +16959,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16985,16 +16988,16 @@
         <v>166</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>81</v>
@@ -17043,7 +17046,7 @@
         <v>81</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
@@ -17061,10 +17064,10 @@
         <v>81</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>81</v>
@@ -17075,10 +17078,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -17101,13 +17104,13 @@
         <v>91</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -17158,7 +17161,7 @@
         <v>81</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>90</v>
@@ -17173,31 +17176,31 @@
         <v>102</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AO118" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
@@ -17216,13 +17219,13 @@
         <v>91</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -17273,7 +17276,7 @@
         <v>81</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
@@ -17288,31 +17291,31 @@
         <v>102</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AO119" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
@@ -17331,13 +17334,13 @@
         <v>91</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -17376,17 +17379,17 @@
         <v>81</v>
       </c>
       <c r="AB120" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AC120" s="2"/>
       <c r="AD120" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE120" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -17401,33 +17404,33 @@
         <v>102</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AO120" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="D121" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
@@ -17446,13 +17449,13 @@
         <v>91</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -17503,7 +17506,7 @@
         <v>81</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
@@ -17518,27 +17521,27 @@
         <v>102</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AO121" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17650,10 +17653,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17765,10 +17768,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17848,7 +17851,7 @@
         <v>81</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
@@ -17880,10 +17883,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17906,17 +17909,17 @@
         <v>91</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>81</v>
@@ -17965,7 +17968,7 @@
         <v>81</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -17986,7 +17989,7 @@
         <v>81</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>81</v>
@@ -17997,10 +18000,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18023,17 +18026,17 @@
         <v>91</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>81</v>
@@ -18082,7 +18085,7 @@
         <v>81</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
@@ -18094,7 +18097,7 @@
         <v>81</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AK126" t="s" s="2">
         <v>81</v>
@@ -18103,7 +18106,7 @@
         <v>81</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>81</v>
@@ -18114,10 +18117,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18229,10 +18232,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18346,10 +18349,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18372,13 +18375,13 @@
         <v>91</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -18417,17 +18420,17 @@
         <v>81</v>
       </c>
       <c r="AB129" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AC129" s="2"/>
       <c r="AD129" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE129" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>79</v>
@@ -18448,7 +18451,7 @@
         <v>81</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>81</v>
@@ -18459,13 +18462,13 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="D130" t="s" s="2">
         <v>81</v>
@@ -18487,13 +18490,13 @@
         <v>91</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -18544,7 +18547,7 @@
         <v>81</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>79</v>
@@ -18565,7 +18568,7 @@
         <v>81</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="AN130" t="s" s="2">
         <v>81</v>
@@ -18576,10 +18579,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18602,19 +18605,19 @@
         <v>91</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>81</v>
@@ -18663,7 +18666,7 @@
         <v>81</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>79</v>
@@ -18684,7 +18687,7 @@
         <v>81</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AN131" t="s" s="2">
         <v>81</v>
@@ -18695,10 +18698,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18721,13 +18724,13 @@
         <v>91</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
@@ -18778,7 +18781,7 @@
         <v>81</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>79</v>
@@ -18799,7 +18802,7 @@
         <v>81</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AN132" t="s" s="2">
         <v>81</v>
@@ -18810,10 +18813,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18836,19 +18839,19 @@
         <v>91</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>81</v>
@@ -18897,7 +18900,7 @@
         <v>81</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
@@ -18918,7 +18921,7 @@
         <v>81</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>81</v>
@@ -18929,10 +18932,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18955,19 +18958,19 @@
         <v>91</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>81</v>
@@ -19016,7 +19019,7 @@
         <v>81</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -19037,7 +19040,7 @@
         <v>81</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AN134" t="s" s="2">
         <v>81</v>
@@ -19048,10 +19051,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -19077,10 +19080,10 @@
         <v>166</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -19110,10 +19113,10 @@
         <v>297</v>
       </c>
       <c r="Y135" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="Z135" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>81</v>
@@ -19131,7 +19134,7 @@
         <v>81</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -19152,7 +19155,7 @@
         <v>81</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AN135" t="s" s="2">
         <v>81</v>
@@ -19163,10 +19166,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19189,13 +19192,13 @@
         <v>91</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -19203,7 +19206,7 @@
         <v>81</v>
       </c>
       <c r="Q136" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="R136" t="s" s="2">
         <v>81</v>
@@ -19248,7 +19251,7 @@
         <v>81</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
@@ -19269,7 +19272,7 @@
         <v>81</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AN136" t="s" s="2">
         <v>81</v>
@@ -19280,10 +19283,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19306,13 +19309,13 @@
         <v>91</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="N137" s="2"/>
       <c r="O137" s="2"/>
@@ -19363,7 +19366,7 @@
         <v>81</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>79</v>
@@ -19384,7 +19387,7 @@
         <v>81</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AN137" t="s" s="2">
         <v>81</v>
@@ -19395,10 +19398,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19421,13 +19424,13 @@
         <v>91</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -19478,7 +19481,7 @@
         <v>81</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>79</v>
@@ -19499,7 +19502,7 @@
         <v>81</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AN138" t="s" s="2">
         <v>81</v>
@@ -19510,10 +19513,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19536,13 +19539,13 @@
         <v>91</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -19593,7 +19596,7 @@
         <v>81</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>79</v>
@@ -19614,7 +19617,7 @@
         <v>81</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AN139" t="s" s="2">
         <v>81</v>
@@ -19625,10 +19628,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19654,10 +19657,10 @@
         <v>166</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -19687,10 +19690,10 @@
         <v>297</v>
       </c>
       <c r="Y140" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="Z140" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>81</v>
@@ -19708,7 +19711,7 @@
         <v>81</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
@@ -19729,7 +19732,7 @@
         <v>81</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AN140" t="s" s="2">
         <v>81</v>
@@ -19740,10 +19743,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19769,13 +19772,13 @@
         <v>166</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -19805,7 +19808,7 @@
       </c>
       <c r="Y141" s="2"/>
       <c r="Z141" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>81</v>
@@ -19823,7 +19826,7 @@
         <v>81</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>79</v>
@@ -19855,10 +19858,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19881,16 +19884,16 @@
         <v>91</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
@@ -19940,7 +19943,7 @@
         <v>81</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>79</v>
@@ -19972,10 +19975,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -20001,16 +20004,16 @@
         <v>166</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>81</v>
@@ -20038,10 +20041,10 @@
         <v>297</v>
       </c>
       <c r="Y143" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="Z143" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="AA143" t="s" s="2">
         <v>81</v>
@@ -20059,7 +20062,7 @@
         <v>81</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
@@ -20080,7 +20083,7 @@
         <v>81</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>81</v>
@@ -20091,10 +20094,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -20117,13 +20120,13 @@
         <v>91</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
@@ -20174,7 +20177,7 @@
         <v>81</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>79</v>
@@ -20195,7 +20198,7 @@
         <v>81</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="AN144" t="s" s="2">
         <v>81</v>
@@ -20206,10 +20209,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20235,13 +20238,13 @@
         <v>235</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
@@ -20270,10 +20273,10 @@
         <v>170</v>
       </c>
       <c r="Y145" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="Z145" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="AA145" t="s" s="2">
         <v>81</v>
@@ -20291,7 +20294,7 @@
         <v>81</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>79</v>
@@ -20312,7 +20315,7 @@
         <v>81</v>
       </c>
       <c r="AM145" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="AN145" t="s" s="2">
         <v>81</v>
@@ -20323,10 +20326,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20349,13 +20352,13 @@
         <v>91</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -20385,10 +20388,10 @@
         <v>156</v>
       </c>
       <c r="Y146" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="Z146" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="AA146" t="s" s="2">
         <v>81</v>
@@ -20406,7 +20409,7 @@
         <v>81</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>79</v>
@@ -20427,25 +20430,25 @@
         <v>81</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="AN146" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO146" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
@@ -20464,13 +20467,13 @@
         <v>91</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" s="2"/>
@@ -20521,7 +20524,7 @@
         <v>81</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>79</v>
@@ -20533,34 +20536,34 @@
         <v>81</v>
       </c>
       <c r="AJ147" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="AK147" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="AN147" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="AO147" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
@@ -20579,16 +20582,16 @@
         <v>91</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
@@ -20638,7 +20641,7 @@
         <v>81</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>79</v>
@@ -20653,31 +20656,31 @@
         <v>102</v>
       </c>
       <c r="AK148" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="AO148" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" t="s" s="2">
@@ -20699,13 +20702,13 @@
         <v>235</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
@@ -20734,10 +20737,10 @@
         <v>156</v>
       </c>
       <c r="Y149" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="Z149" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>81</v>
@@ -20755,7 +20758,7 @@
         <v>81</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>79</v>
@@ -20770,16 +20773,16 @@
         <v>102</v>
       </c>
       <c r="AK149" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>81</v>
@@ -20787,14 +20790,14 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" t="s" s="2">
@@ -20813,16 +20816,16 @@
         <v>91</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -20872,7 +20875,7 @@
         <v>81</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>79</v>
@@ -20887,16 +20890,16 @@
         <v>102</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="AO150" t="s" s="2">
         <v>81</v>
@@ -20904,10 +20907,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20933,10 +20936,10 @@
         <v>235</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
@@ -20966,10 +20969,10 @@
         <v>156</v>
       </c>
       <c r="Y151" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="Z151" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="AA151" t="s" s="2">
         <v>81</v>
@@ -20987,7 +20990,7 @@
         <v>81</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>79</v>
@@ -21008,10 +21011,10 @@
         <v>81</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="AO151" t="s" s="2">
         <v>81</v>
@@ -21019,10 +21022,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -21045,13 +21048,13 @@
         <v>91</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -21102,7 +21105,7 @@
         <v>81</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>79</v>
@@ -21123,10 +21126,10 @@
         <v>81</v>
       </c>
       <c r="AM152" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="AO152" t="s" s="2">
         <v>81</v>
@@ -21134,10 +21137,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21163,13 +21166,13 @@
         <v>235</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
@@ -21198,10 +21201,10 @@
         <v>156</v>
       </c>
       <c r="Y153" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="Z153" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="AA153" t="s" s="2">
         <v>81</v>
@@ -21219,7 +21222,7 @@
         <v>81</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>79</v>
@@ -21234,16 +21237,16 @@
         <v>102</v>
       </c>
       <c r="AK153" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="AL153" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="AM153" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>81</v>
@@ -21251,10 +21254,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21277,16 +21280,16 @@
         <v>91</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
@@ -21336,7 +21339,7 @@
         <v>81</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>79</v>
@@ -21351,16 +21354,16 @@
         <v>102</v>
       </c>
       <c r="AK154" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="AN154" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="AO154" t="s" s="2">
         <v>81</v>
@@ -21368,10 +21371,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21394,13 +21397,13 @@
         <v>81</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
@@ -21451,7 +21454,7 @@
         <v>81</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>79</v>
@@ -21466,13 +21469,13 @@
         <v>102</v>
       </c>
       <c r="AK155" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="AL155" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="AN155" t="s" s="2">
         <v>81</v>
@@ -21483,14 +21486,14 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
@@ -21509,16 +21512,16 @@
         <v>81</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
@@ -21568,7 +21571,7 @@
         <v>81</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>79</v>
@@ -21583,13 +21586,13 @@
         <v>102</v>
       </c>
       <c r="AK156" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="AM156" t="s" s="2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="AN156" t="s" s="2">
         <v>81</v>
@@ -21600,10 +21603,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21626,16 +21629,16 @@
         <v>91</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
@@ -21685,7 +21688,7 @@
         <v>81</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>79</v>
@@ -21703,10 +21706,10 @@
         <v>81</v>
       </c>
       <c r="AL157" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="AM157" t="s" s="2">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="AN157" t="s" s="2">
         <v>81</v>
@@ -21717,14 +21720,14 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="E158" s="2"/>
       <c r="F158" t="s" s="2">
@@ -21746,16 +21749,16 @@
         <v>235</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="O158" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>81</v>
@@ -21783,10 +21786,10 @@
         <v>156</v>
       </c>
       <c r="Y158" t="s" s="2">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="Z158" t="s" s="2">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="AA158" t="s" s="2">
         <v>81</v>
@@ -21804,7 +21807,7 @@
         <v>81</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>79</v>
@@ -21822,24 +21825,24 @@
         <v>81</v>
       </c>
       <c r="AL158" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="AN158" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO158" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21951,10 +21954,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -22068,13 +22071,13 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
+        <v>911</v>
+      </c>
+      <c r="B161" t="s" s="2">
         <v>910</v>
       </c>
-      <c r="B161" t="s" s="2">
-        <v>909</v>
-      </c>
       <c r="C161" t="s" s="2">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="D161" t="s" s="2">
         <v>81</v>
@@ -22096,13 +22099,13 @@
         <v>81</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
@@ -22185,10 +22188,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22304,10 +22307,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22423,10 +22426,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22449,13 +22452,13 @@
         <v>81</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="L164" t="s" s="2">
         <v>50</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" s="2"/>
@@ -22506,7 +22509,7 @@
         <v>81</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>79</v>
@@ -22521,27 +22524,27 @@
         <v>102</v>
       </c>
       <c r="AK164" t="s" s="2">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="AL164" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AM164" t="s" s="2">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="AN164" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO164" t="s" s="2">
-        <v>922</v>
+        <v>923</v>
       </c>
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22653,10 +22656,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22770,13 +22773,13 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
+        <v>926</v>
+      </c>
+      <c r="B167" t="s" s="2">
         <v>925</v>
       </c>
-      <c r="B167" t="s" s="2">
-        <v>924</v>
-      </c>
       <c r="C167" t="s" s="2">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="D167" t="s" s="2">
         <v>81</v>
@@ -22798,13 +22801,13 @@
         <v>81</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="L167" t="s" s="2">
         <v>63</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
@@ -22887,10 +22890,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -23002,10 +23005,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -23117,10 +23120,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23160,7 +23163,7 @@
       </c>
       <c r="Q170" s="2"/>
       <c r="R170" t="s" s="2">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="S170" t="s" s="2">
         <v>81</v>
@@ -23234,10 +23237,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23297,7 +23300,7 @@
       </c>
       <c r="Y171" s="2"/>
       <c r="Z171" t="s" s="2">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="AA171" t="s" s="2">
         <v>81</v>
@@ -23347,10 +23350,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23373,16 +23376,16 @@
         <v>91</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
@@ -23432,7 +23435,7 @@
         <v>81</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>79</v>
@@ -23453,7 +23456,7 @@
         <v>189</v>
       </c>
       <c r="AM172" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="AN172" t="s" s="2">
         <v>81</v>
@@ -23464,10 +23467,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23490,13 +23493,13 @@
         <v>91</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" s="2"/>
@@ -23547,7 +23550,7 @@
         <v>81</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>79</v>
@@ -23568,7 +23571,7 @@
         <v>189</v>
       </c>
       <c r="AM173" t="s" s="2">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="AN173" t="s" s="2">
         <v>81</v>
@@ -23579,10 +23582,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23605,13 +23608,13 @@
         <v>91</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="N174" s="2"/>
       <c r="O174" s="2"/>
@@ -23662,7 +23665,7 @@
         <v>81</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>90</v>
@@ -23683,7 +23686,7 @@
         <v>189</v>
       </c>
       <c r="AM174" t="s" s="2">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="AN174" t="s" s="2">
         <v>81</v>
@@ -23694,10 +23697,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23723,10 +23726,10 @@
         <v>104</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="N175" s="2"/>
       <c r="O175" s="2"/>
@@ -23777,7 +23780,7 @@
         <v>81</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>79</v>
@@ -23795,10 +23798,10 @@
         <v>81</v>
       </c>
       <c r="AL175" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AM175" t="s" s="2">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="AN175" t="s" s="2">
         <v>81</v>
@@ -23809,10 +23812,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23835,16 +23838,16 @@
         <v>81</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="O176" s="2"/>
       <c r="P176" t="s" s="2">
@@ -23894,7 +23897,7 @@
         <v>81</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>79</v>
@@ -23909,13 +23912,13 @@
         <v>102</v>
       </c>
       <c r="AK176" t="s" s="2">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="AL176" t="s" s="2">
         <v>189</v>
       </c>
       <c r="AM176" t="s" s="2">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="AN176" t="s" s="2">
         <v>81</v>

--- a/branches/release-3.0.0/StructureDefinition-ereferral-servicerequest-nursing.xlsx
+++ b/branches/release-3.0.0/StructureDefinition-ereferral-servicerequest-nursing.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T04:33:29+00:00</t>
+    <t>2026-10-29T04:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release-3.0.0/StructureDefinition-ereferral-servicerequest-nursing.xlsx
+++ b/branches/release-3.0.0/StructureDefinition-ereferral-servicerequest-nursing.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T04:45:11+00:00</t>
+    <t>2026-10-29T06:41:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release-3.0.0/StructureDefinition-ereferral-servicerequest-nursing.xlsx
+++ b/branches/release-3.0.0/StructureDefinition-ereferral-servicerequest-nursing.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T06:41:01+00:00</t>
+    <t>2026-10-29T06:43:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release-3.0.0/StructureDefinition-ereferral-servicerequest-nursing.xlsx
+++ b/branches/release-3.0.0/StructureDefinition-ereferral-servicerequest-nursing.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T06:43:17+00:00</t>
+    <t>2026-10-29T07:36:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release-3.0.0/StructureDefinition-ereferral-servicerequest-nursing.xlsx
+++ b/branches/release-3.0.0/StructureDefinition-ereferral-servicerequest-nursing.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T07:36:53+00:00</t>
+    <t>2026-10-29T08:00:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
